--- a/docs/modele-import-agents.xlsx
+++ b/docs/modele-import-agents.xlsx
@@ -62,7 +62,7 @@
     <t>Cadre A1</t>
   </si>
   <si>
-    <t>ORDRE_1</t>
+    <t>INDICE_SUP_800</t>
   </si>
   <si>
     <t>0197984877</t>
@@ -83,7 +83,7 @@
     <t>Cadre A2</t>
   </si>
   <si>
-    <t>ORDRE_2</t>
+    <t>INDICE_400_799</t>
   </si>
   <si>
     <t>0167267455</t>
@@ -104,7 +104,7 @@
     <t>Agent</t>
   </si>
   <si>
-    <t>ORDRE_3</t>
+    <t>INDICE_INF_400</t>
   </si>
   <si>
     <t>0155112233</t>
@@ -496,16 +496,16 @@
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="17.567" customWidth="true" style="0"/>
+    <col min="2" max="2" width="13.997" customWidth="true" style="0"/>
+    <col min="3" max="3" width="11.711" customWidth="true" style="0"/>
+    <col min="4" max="4" width="16.425" customWidth="true" style="0"/>
+    <col min="5" max="5" width="15.282" customWidth="true" style="0"/>
+    <col min="6" max="6" width="8.141" customWidth="true" style="0"/>
+    <col min="7" max="7" width="15.282" customWidth="true" style="0"/>
+    <col min="8" max="8" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="12.854" customWidth="true" style="0"/>
+    <col min="10" max="10" width="11.711" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
